--- a/sds_service/training/data/speech_mvp_dataset.xlsx
+++ b/sds_service/training/data/speech_mvp_dataset.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kasun\Documents\GitHub\speech-delivery-score-mvp\training\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E2C852-ECED-4A63-BF65-CE97FB57A0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -40,9 +46,6 @@
     <t>Avg_Pause</t>
   </si>
   <si>
-    <t>Pitch_Variability</t>
-  </si>
-  <si>
     <t>Disfluencies</t>
   </si>
   <si>
@@ -50,9 +53,6 @@
   </si>
   <si>
     <t>Loudness_Variance</t>
-  </si>
-  <si>
-    <t>Articulation_Rate</t>
   </si>
   <si>
     <t>Good</t>
@@ -63,12 +63,18 @@
   <si>
     <t>Excellent</t>
   </si>
+  <si>
+    <t>pitch_variability</t>
+  </si>
+  <si>
+    <t>articulation_rate</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,24 +126,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,7 +198,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -209,6 +232,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -243,9 +267,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -418,11 +443,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" customWidth="1"/>
+    <col min="11" max="11" width="13.77734375" customWidth="1"/>
+    <col min="12" max="12" width="21.77734375" customWidth="1"/>
+    <col min="13" max="13" width="41.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,66 +487,66 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>141.30570602357261</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.54615731448739646</v>
+      </c>
+      <c r="I2" s="2">
+        <v>4.9543543384089226</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>3.0248621707982151E-3</v>
+      </c>
+      <c r="M2" s="4">
+        <v>3.4576531521936991</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>141.3057060235726</v>
-      </c>
-      <c r="H2">
-        <v>0.2260794119627306</v>
-      </c>
-      <c r="I2">
-        <v>51.10112931842603</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>0.003024862170798215</v>
-      </c>
-      <c r="M2">
-        <v>2.336351573486512</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -526,11 +566,11 @@
       <c r="G3">
         <v>101.4626241192055</v>
       </c>
-      <c r="H3">
-        <v>0.08896779826526655</v>
-      </c>
-      <c r="I3">
-        <v>20.25751154785342</v>
+      <c r="H3" s="6">
+        <v>0.79483866930866021</v>
+      </c>
+      <c r="I3" s="2">
+        <v>3.3226182694246789</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -539,15 +579,15 @@
         <v>5</v>
       </c>
       <c r="L3">
-        <v>0.006602440107067964</v>
-      </c>
-      <c r="M3">
-        <v>1.492370885852772</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>6.6024401070679641E-3</v>
+      </c>
+      <c r="M3" s="4">
+        <v>4.5095739418742884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -565,13 +605,13 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>134.0672532262956</v>
-      </c>
-      <c r="H4">
-        <v>0.2268690514824046</v>
-      </c>
-      <c r="I4">
-        <v>55.43523591840211</v>
+        <v>134.06725322629561</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.81432137086830769</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3.135772556695577</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -580,15 +620,15 @@
         <v>2</v>
       </c>
       <c r="L4">
-        <v>0.006667878183297869</v>
-      </c>
-      <c r="M4">
-        <v>2.394434758646508</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>6.6678781832978694E-3</v>
+      </c>
+      <c r="M4" s="4">
+        <v>4.000566168112031</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -608,11 +648,11 @@
       <c r="G5">
         <v>114.8974306701466</v>
       </c>
-      <c r="H5">
-        <v>0.214658718141919</v>
-      </c>
-      <c r="I5">
-        <v>48.99001897782587</v>
+      <c r="H5" s="6">
+        <v>0.6994306826945953</v>
+      </c>
+      <c r="I5" s="2">
+        <v>5.160111366248171</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -621,15 +661,15 @@
         <v>3</v>
       </c>
       <c r="L5">
-        <v>0.01131745704672621</v>
-      </c>
-      <c r="M5">
-        <v>2.769533513014833</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>1.1317457046726209E-2</v>
+      </c>
+      <c r="M5" s="4">
+        <v>3.6046490941895231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -649,11 +689,11 @@
       <c r="G6">
         <v>141.9817215665031</v>
       </c>
-      <c r="H6">
-        <v>0.4192007859466339</v>
-      </c>
-      <c r="I6">
-        <v>84.05205305878188</v>
+      <c r="H6" s="6">
+        <v>0.85967857208349774</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1.762924065027861</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -662,15 +702,15 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.006392325753491903</v>
-      </c>
-      <c r="M6">
-        <v>2.601313503559335</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>6.3923257534919033E-3</v>
+      </c>
+      <c r="M6" s="4">
+        <v>5.485833653243712</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -688,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="G7">
-        <v>159.2316260834195</v>
-      </c>
-      <c r="H7">
-        <v>0.2951623850711405</v>
-      </c>
-      <c r="I7">
-        <v>63.17698436079728</v>
+        <v>159.23162608341951</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1.0010127142036349</v>
+      </c>
+      <c r="I7" s="2">
+        <v>5.3700322805426719</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -703,15 +743,15 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>0.005428012840989428</v>
-      </c>
-      <c r="M7">
-        <v>2.206060226986481</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>5.4280128409894277E-3</v>
+      </c>
+      <c r="M7" s="4">
+        <v>3.7016618518720001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -729,13 +769,13 @@
         <v>4</v>
       </c>
       <c r="G8">
-        <v>146.4325497423181</v>
-      </c>
-      <c r="H8">
-        <v>0.3778060899266982</v>
-      </c>
-      <c r="I8">
-        <v>80.43860610918658</v>
+        <v>146.43254974231809</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1.371546475302633</v>
+      </c>
+      <c r="I8" s="2">
+        <v>3.4976757579236919</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -744,15 +784,15 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.005526448161334695</v>
-      </c>
-      <c r="M8">
-        <v>2.635101808434221</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>5.5264481613346954E-3</v>
+      </c>
+      <c r="M8" s="4">
+        <v>4.8002617486301808</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -770,13 +810,13 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>105.8826656580899</v>
-      </c>
-      <c r="H9">
-        <v>0.08986027544282733</v>
-      </c>
-      <c r="I9">
-        <v>12.30078464702805</v>
+        <v>105.88266565808991</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.94364445320795975</v>
+      </c>
+      <c r="I9" s="2">
+        <v>3.795437171009703</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -785,15 +825,15 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>0.01198057222139588</v>
-      </c>
-      <c r="M9">
-        <v>1.746670677493638</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>1.1980572221395879E-2</v>
+      </c>
+      <c r="M9" s="4">
+        <v>5.0726651346726293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -813,11 +853,11 @@
       <c r="G10">
         <v>146.3672936608468</v>
       </c>
-      <c r="H10">
-        <v>0.3252428467969608</v>
-      </c>
-      <c r="I10">
-        <v>39.5883069202475</v>
+      <c r="H10" s="6">
+        <v>0.96438759768069116</v>
+      </c>
+      <c r="I10" s="2">
+        <v>3.1176573988798459</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -826,15 +866,15 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>0.007291723704856619</v>
-      </c>
-      <c r="M10">
-        <v>2.376869487175769</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>7.2917237048566192E-3</v>
+      </c>
+      <c r="M10" s="4">
+        <v>3.158023797405594</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -854,11 +894,11 @@
       <c r="G11">
         <v>145.1172796222497</v>
       </c>
-      <c r="H11">
-        <v>0.3540276118397232</v>
-      </c>
-      <c r="I11">
-        <v>33.8777148311908</v>
+      <c r="H11" s="6">
+        <v>0.88138852105845822</v>
+      </c>
+      <c r="I11" s="2">
+        <v>3.7518045144641872</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -867,15 +907,15 @@
         <v>3</v>
       </c>
       <c r="L11">
-        <v>0.006976833360436013</v>
-      </c>
-      <c r="M11">
-        <v>2.457179611534357</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>6.9768333604360126E-3</v>
+      </c>
+      <c r="M11" s="4">
+        <v>4.1443777784441407</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>5</v>
@@ -893,13 +933,13 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>154.7323762457355</v>
-      </c>
-      <c r="H12">
-        <v>0.3463585543671563</v>
-      </c>
-      <c r="I12">
-        <v>61.53206281931595</v>
+        <v>154.73237624573551</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.42030719617523971</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5.0711382259809143</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -908,15 +948,15 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0.003485152775314135</v>
-      </c>
-      <c r="M12">
-        <v>2.842021848072791</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>3.485152775314135E-3</v>
+      </c>
+      <c r="M12" s="4">
+        <v>3.7894798094550648</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -936,11 +976,11 @@
       <c r="G13">
         <v>111.8495774310219</v>
       </c>
-      <c r="H13">
-        <v>0.2135112550901979</v>
-      </c>
-      <c r="I13">
-        <v>8.796986949392718</v>
+      <c r="H13" s="6">
+        <v>0.89337153113769585</v>
+      </c>
+      <c r="I13" s="2">
+        <v>4.5708631014640391</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -949,15 +989,15 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>0.005794264223637391</v>
-      </c>
-      <c r="M13">
-        <v>1.695802712168962</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>5.7942642236373911E-3</v>
+      </c>
+      <c r="M13" s="4">
+        <v>3.7406453620643978</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -975,13 +1015,13 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>138.7471265666705</v>
-      </c>
-      <c r="H14">
-        <v>0.1507306372740632</v>
-      </c>
-      <c r="I14">
-        <v>44.96321991958128</v>
+        <v>138.74712656667049</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.91505755248525666</v>
+      </c>
+      <c r="I14" s="2">
+        <v>4.2926864838004049</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -990,15 +1030,15 @@
         <v>3</v>
       </c>
       <c r="L14">
-        <v>0.01595281044201645</v>
-      </c>
-      <c r="M14">
-        <v>2.174504076149805</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>1.5952810442016449E-2</v>
+      </c>
+      <c r="M14" s="4">
+        <v>4.433226090084144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -1018,11 +1058,11 @@
       <c r="G15">
         <v>133.8728412881035</v>
       </c>
-      <c r="H15">
-        <v>0.3677209792559831</v>
-      </c>
-      <c r="I15">
-        <v>51.19687411547444</v>
+      <c r="H15" s="6">
+        <v>1.515810528121321</v>
+      </c>
+      <c r="I15" s="2">
+        <v>3.8888730061317429</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1031,15 +1071,15 @@
         <v>1</v>
       </c>
       <c r="L15">
-        <v>0.004952356288842955</v>
-      </c>
-      <c r="M15">
-        <v>2.803738891543556</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>4.9523562888429554E-3</v>
+      </c>
+      <c r="M15" s="4">
+        <v>3.7262777021460289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -1057,13 +1097,13 @@
         <v>5</v>
       </c>
       <c r="G16">
-        <v>171.4394408932532</v>
-      </c>
-      <c r="H16">
-        <v>0.3816959511159005</v>
-      </c>
-      <c r="I16">
-        <v>49.74857413342393</v>
+        <v>171.43944089325319</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0.85190975880471942</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2.3543900275279168</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1072,15 +1112,15 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0.005186454314769428</v>
-      </c>
-      <c r="M16">
-        <v>2.545636184448649</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>5.1864543147694276E-3</v>
+      </c>
+      <c r="M16" s="4">
+        <v>3.8024185722041168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -1100,11 +1140,11 @@
       <c r="G17">
         <v>166.6130173060815</v>
       </c>
-      <c r="H17">
-        <v>0.3340322461092611</v>
-      </c>
-      <c r="I17">
-        <v>67.95383494522412</v>
+      <c r="H17" s="6">
+        <v>0.97538683558340311</v>
+      </c>
+      <c r="I17" s="2">
+        <v>2.9558630864822599</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1113,15 +1153,15 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>0.007134641248007408</v>
-      </c>
-      <c r="M17">
-        <v>2.745369764396158</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>7.1346412480074077E-3</v>
+      </c>
+      <c r="M17" s="4">
+        <v>3.9991310626248229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -1141,11 +1181,11 @@
       <c r="G18">
         <v>129.0388789515552</v>
       </c>
-      <c r="H18">
-        <v>0.1476064213389496</v>
-      </c>
-      <c r="I18">
-        <v>47.15129646551997</v>
+      <c r="H18" s="6">
+        <v>0.89132205757368921</v>
+      </c>
+      <c r="I18" s="2">
+        <v>3.4567987633688322</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1154,15 +1194,15 @@
         <v>2</v>
       </c>
       <c r="L18">
-        <v>0.01074401136094461</v>
-      </c>
-      <c r="M18">
-        <v>1.801511528532705</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>1.074401136094461E-2</v>
+      </c>
+      <c r="M18" s="4">
+        <v>3.8759604389740581</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -1182,11 +1222,11 @@
       <c r="G19">
         <v>120.4971073760984</v>
       </c>
-      <c r="H19">
-        <v>0.2501450888955741</v>
-      </c>
-      <c r="I19">
-        <v>59.07122338149983</v>
+      <c r="H19" s="6">
+        <v>0.60783049059511707</v>
+      </c>
+      <c r="I19" s="2">
+        <v>4.2576764544288386</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -1195,15 +1235,15 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>0.007962435456856255</v>
-      </c>
-      <c r="M19">
-        <v>2.540117151818666</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>7.9624354568562546E-3</v>
+      </c>
+      <c r="M19" s="4">
+        <v>3.395857875792724</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -1223,11 +1263,11 @@
       <c r="G20">
         <v>132.7035085092146</v>
       </c>
-      <c r="H20">
-        <v>0.2666078609028576</v>
-      </c>
-      <c r="I20">
-        <v>60.61988560623999</v>
+      <c r="H20" s="6">
+        <v>1.185705703628755</v>
+      </c>
+      <c r="I20" s="2">
+        <v>3.8696526645188789</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1236,15 +1276,15 @@
         <v>2</v>
       </c>
       <c r="L20">
-        <v>0.006070940502710065</v>
-      </c>
-      <c r="M20">
-        <v>2.685603328154008</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>6.0709405027100649E-3</v>
+      </c>
+      <c r="M20" s="4">
+        <v>4.5775439029084843</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B21">
         <v>5</v>
@@ -1262,13 +1302,13 @@
         <v>5</v>
       </c>
       <c r="G21">
-        <v>164.5255024746237</v>
-      </c>
-      <c r="H21">
-        <v>0.3525371979427633</v>
-      </c>
-      <c r="I21">
-        <v>74.94599891881714</v>
+        <v>164.52550247462369</v>
+      </c>
+      <c r="H21" s="6">
+        <v>1.0879832581716939</v>
+      </c>
+      <c r="I21" s="2">
+        <v>4.7835043063584646</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1277,57 +1317,57 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0.006610820309392503</v>
-      </c>
-      <c r="M21">
-        <v>2.805592085405295</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>6.6108203093925028E-3</v>
+      </c>
+      <c r="M21" s="4">
+        <v>4.72911856310456</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>148.20646071755061</v>
+      </c>
+      <c r="H22" s="6">
+        <v>1.0977579867607621</v>
+      </c>
+      <c r="I22" s="2">
+        <v>4.2736273877275641</v>
+      </c>
+      <c r="J22">
+        <v>2</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>9.1975537039743795E-3</v>
+      </c>
+      <c r="M22" s="4">
+        <v>4.30617115372113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>13</v>
       </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22">
-        <v>4</v>
-      </c>
-      <c r="G22">
-        <v>148.2064607175506</v>
-      </c>
-      <c r="H22">
-        <v>0.2338245878052885</v>
-      </c>
-      <c r="I22">
-        <v>47.38782556127336</v>
-      </c>
-      <c r="J22">
-        <v>2</v>
-      </c>
-      <c r="K22">
-        <v>3</v>
-      </c>
-      <c r="L22">
-        <v>0.009197553703974379</v>
-      </c>
-      <c r="M22">
-        <v>2.328232560639073</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
       <c r="B23">
         <v>4</v>
       </c>
@@ -1344,13 +1384,13 @@
         <v>5</v>
       </c>
       <c r="G23">
-        <v>158.5397471106785</v>
-      </c>
-      <c r="H23">
-        <v>0.3696020944866298</v>
-      </c>
-      <c r="I23">
-        <v>68.75474752406316</v>
+        <v>158.53974711067849</v>
+      </c>
+      <c r="H23" s="6">
+        <v>0.67265313630131529</v>
+      </c>
+      <c r="I23" s="2">
+        <v>3.8543505779385709</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -1359,15 +1399,15 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0.004146740057962024</v>
-      </c>
-      <c r="M23">
-        <v>2.697143890458981</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>4.1467400579620244E-3</v>
+      </c>
+      <c r="M23" s="4">
+        <v>3.87406840938664</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -1387,11 +1427,11 @@
       <c r="G24">
         <v>161.5811087350007</v>
       </c>
-      <c r="H24">
-        <v>0.3895831346981468</v>
-      </c>
-      <c r="I24">
-        <v>76.24119817052156</v>
+      <c r="H24" s="6">
+        <v>1.2506985777340249</v>
+      </c>
+      <c r="I24" s="2">
+        <v>6.0757612975672028</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -1400,385 +1440,385 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0.00562834550926428</v>
-      </c>
-      <c r="M24">
-        <v>2.715160911638745</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>5.6283455092642799E-3</v>
+      </c>
+      <c r="M24" s="4">
+        <v>3.6768735582021308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>4</v>
+      </c>
+      <c r="G25">
+        <v>129.84257432731829</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0.5495372343019298</v>
+      </c>
+      <c r="I25" s="2">
+        <v>4.2062266850499279</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>3.8366921487709088E-3</v>
+      </c>
+      <c r="M25" s="4">
+        <v>3.6778279622441321</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>129.22333668121351</v>
+      </c>
+      <c r="H26" s="6">
+        <v>1.0467142734500681</v>
+      </c>
+      <c r="I26" s="2">
+        <v>3.3680577983916282</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>9.9507124338991046E-3</v>
+      </c>
+      <c r="M26" s="4">
+        <v>5.5144258190196247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27">
+        <v>139.27706771696279</v>
+      </c>
+      <c r="H27" s="6">
+        <v>1.4476139064524951</v>
+      </c>
+      <c r="I27" s="2">
+        <v>5.6599670064869301</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>1.8713160370786119E-3</v>
+      </c>
+      <c r="M27" s="4">
+        <v>4.6627029809399856</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>13</v>
       </c>
-      <c r="B25">
-        <v>4</v>
-      </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>129.8425743273183</v>
-      </c>
-      <c r="H25">
-        <v>0.3211187435421723</v>
-      </c>
-      <c r="I25">
-        <v>55.9527707987105</v>
-      </c>
-      <c r="J25">
-        <v>2</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>0.003836692148770909</v>
-      </c>
-      <c r="M25">
-        <v>2.423702704273217</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>152.24092481810419</v>
+      </c>
+      <c r="H28" s="6">
+        <v>0.65236591871732796</v>
+      </c>
+      <c r="I28" s="2">
+        <v>5.000411548413398</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>4.2269902161445336E-3</v>
+      </c>
+      <c r="M28" s="4">
+        <v>3.5959339528499972</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>128.48978655667929</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0.75842556759930702</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5.6160877902438147</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>4.5817552208780293E-3</v>
+      </c>
+      <c r="M29" s="4">
+        <v>4.1988186964622836</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+      <c r="G30">
+        <v>145.12633963665741</v>
+      </c>
+      <c r="H30" s="6">
+        <v>0.92491284127191031</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3.6890680643704901</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="L30">
+        <v>5.8461926886751942E-3</v>
+      </c>
+      <c r="M30" s="4">
+        <v>3.882478984940382</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>13</v>
       </c>
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>129.2233366812135</v>
-      </c>
-      <c r="H26">
-        <v>0.2329242278630522</v>
-      </c>
-      <c r="I26">
-        <v>53.73089078717606</v>
-      </c>
-      <c r="J26">
-        <v>2</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>0.009950712433899105</v>
-      </c>
-      <c r="M26">
-        <v>2.195297219663954</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
+      <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>145.30824347895299</v>
+      </c>
+      <c r="H31" s="6">
+        <v>0.77413108647095019</v>
+      </c>
+      <c r="I31" s="2">
+        <v>4.7763091264811024</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>5.3424569180075144E-3</v>
+      </c>
+      <c r="M31" s="4">
+        <v>4.4502802256937741</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>4</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>4</v>
+      </c>
+      <c r="G32">
+        <v>133.24901792781131</v>
+      </c>
+      <c r="H32" s="6">
+        <v>0.51233414223346685</v>
+      </c>
+      <c r="I32" s="2">
+        <v>2.3471505409276392</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32">
+        <v>3</v>
+      </c>
+      <c r="L32">
+        <v>6.7152410299574144E-3</v>
+      </c>
+      <c r="M32" s="4">
+        <v>4.4260994616736049</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>13</v>
       </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27">
-        <v>4</v>
-      </c>
-      <c r="F27">
-        <v>3</v>
-      </c>
-      <c r="G27">
-        <v>139.2770677169628</v>
-      </c>
-      <c r="H27">
-        <v>0.3172136927422741</v>
-      </c>
-      <c r="I27">
-        <v>63.60010430082888</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>2</v>
-      </c>
-      <c r="L27">
-        <v>0.001871316037078612</v>
-      </c>
-      <c r="M27">
-        <v>2.74281776498815</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28">
-        <v>5</v>
-      </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28">
-        <v>5</v>
-      </c>
-      <c r="E28">
-        <v>4</v>
-      </c>
-      <c r="F28">
-        <v>4</v>
-      </c>
-      <c r="G28">
-        <v>152.2409248181042</v>
-      </c>
-      <c r="H28">
-        <v>0.3506296200390897</v>
-      </c>
-      <c r="I28">
-        <v>70.97676098548831</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>0.004226990216144534</v>
-      </c>
-      <c r="M28">
-        <v>3.130636491502312</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" t="s">
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>5</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33">
+        <v>170.47398921130241</v>
+      </c>
+      <c r="H33" s="6">
+        <v>0.91714074370150689</v>
+      </c>
+      <c r="I33" s="2">
+        <v>4.5840064109141681</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>5.2031135479465064E-3</v>
+      </c>
+      <c r="M33" s="4">
+        <v>4.7501657923432834</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>13</v>
       </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>4</v>
-      </c>
-      <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="G29">
-        <v>128.4897865566793</v>
-      </c>
-      <c r="H29">
-        <v>0.2385373393026336</v>
-      </c>
-      <c r="I29">
-        <v>42.79274382500498</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <v>0.004581755220878029</v>
-      </c>
-      <c r="M29">
-        <v>2.876743239660765</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30">
-        <v>3</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30">
-        <v>3</v>
-      </c>
-      <c r="F30">
-        <v>3</v>
-      </c>
-      <c r="G30">
-        <v>145.1263396366574</v>
-      </c>
-      <c r="H30">
-        <v>0.4000936671372709</v>
-      </c>
-      <c r="I30">
-        <v>61.40508605823261</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>5</v>
-      </c>
-      <c r="L30">
-        <v>0.005846192688675194</v>
-      </c>
-      <c r="M30">
-        <v>2.753832036216386</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31">
-        <v>4</v>
-      </c>
-      <c r="C31">
-        <v>5</v>
-      </c>
-      <c r="D31">
-        <v>4</v>
-      </c>
-      <c r="E31">
-        <v>4</v>
-      </c>
-      <c r="F31">
-        <v>4</v>
-      </c>
-      <c r="G31">
-        <v>145.308243478953</v>
-      </c>
-      <c r="H31">
-        <v>0.3192107077616144</v>
-      </c>
-      <c r="I31">
-        <v>84.36183468077766</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0.005342456918007514</v>
-      </c>
-      <c r="M31">
-        <v>3.082305921301886</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32">
-        <v>4</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32">
-        <v>4</v>
-      </c>
-      <c r="F32">
-        <v>4</v>
-      </c>
-      <c r="G32">
-        <v>133.2490179278113</v>
-      </c>
-      <c r="H32">
-        <v>0.2998279945877999</v>
-      </c>
-      <c r="I32">
-        <v>37.18855484740887</v>
-      </c>
-      <c r="J32">
-        <v>2</v>
-      </c>
-      <c r="K32">
-        <v>3</v>
-      </c>
-      <c r="L32">
-        <v>0.006715241029957414</v>
-      </c>
-      <c r="M32">
-        <v>2.472700105824934</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33">
-        <v>5</v>
-      </c>
-      <c r="C33">
-        <v>5</v>
-      </c>
-      <c r="D33">
-        <v>5</v>
-      </c>
-      <c r="E33">
-        <v>5</v>
-      </c>
-      <c r="F33">
-        <v>4</v>
-      </c>
-      <c r="G33">
-        <v>170.4739892113024</v>
-      </c>
-      <c r="H33">
-        <v>0.3218370694269818</v>
-      </c>
-      <c r="I33">
-        <v>95.39257791210892</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="L33">
-        <v>0.005203113547946506</v>
-      </c>
-      <c r="M33">
-        <v>2.709914545859881</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
       <c r="B34">
         <v>5</v>
       </c>
@@ -1795,13 +1835,13 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>158.8606356024615</v>
-      </c>
-      <c r="H34">
-        <v>0.3431461089479073</v>
-      </c>
-      <c r="I34">
-        <v>72.00134419173423</v>
+        <v>158.86063560246151</v>
+      </c>
+      <c r="H34" s="6">
+        <v>0.6344240715684738</v>
+      </c>
+      <c r="I34" s="2">
+        <v>3.6422760417458959</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -1810,15 +1850,15 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>0.00282913417186959</v>
-      </c>
-      <c r="M34">
-        <v>2.697056348273013</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>2.8291341718695898E-3</v>
+      </c>
+      <c r="M34" s="4">
+        <v>3.5896661248026822</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -1838,11 +1878,11 @@
       <c r="G35">
         <v>125.9281085939265</v>
       </c>
-      <c r="H35">
-        <v>-0.002316087047176091</v>
-      </c>
-      <c r="I35">
-        <v>43.08872810863878</v>
+      <c r="H35" s="6">
+        <v>1.0183981076587949</v>
+      </c>
+      <c r="I35" s="2">
+        <v>2.444942044482068</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -1851,15 +1891,15 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>0.01598846088759128</v>
-      </c>
-      <c r="M35">
-        <v>1.805872503237099</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>1.5988460887591281E-2</v>
+      </c>
+      <c r="M35" s="4">
+        <v>4.1628411791828777</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -1877,13 +1917,13 @@
         <v>1</v>
       </c>
       <c r="G36">
-        <v>99.39484763255118</v>
-      </c>
-      <c r="H36">
-        <v>0.07071271677376557</v>
-      </c>
-      <c r="I36">
-        <v>23.39454460068163</v>
+        <v>99.394847632551176</v>
+      </c>
+      <c r="H36" s="6">
+        <v>0.67014394144154921</v>
+      </c>
+      <c r="I36" s="2">
+        <v>4.8326004040179766</v>
       </c>
       <c r="J36">
         <v>2</v>
@@ -1892,15 +1932,15 @@
         <v>4</v>
       </c>
       <c r="L36">
-        <v>0.007859030710322503</v>
-      </c>
-      <c r="M36">
-        <v>1.855068780123668</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>7.8590307103225034E-3</v>
+      </c>
+      <c r="M36" s="4">
+        <v>3.0508718090254838</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1918,13 +1958,13 @@
         <v>1</v>
       </c>
       <c r="G37">
-        <v>105.5806080093355</v>
-      </c>
-      <c r="H37">
-        <v>0.1523751481997747</v>
-      </c>
-      <c r="I37">
-        <v>29.73453965021858</v>
+        <v>105.58060800933551</v>
+      </c>
+      <c r="H37" s="6">
+        <v>1.2874836012543851</v>
+      </c>
+      <c r="I37" s="2">
+        <v>1.989868675003984</v>
       </c>
       <c r="J37">
         <v>5</v>
@@ -1933,57 +1973,57 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <v>0.01056716319803688</v>
-      </c>
-      <c r="M37">
-        <v>2.260745374807155</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>1.056716319803688E-2</v>
+      </c>
+      <c r="M37" s="4">
+        <v>3.3455958197426932</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38">
+        <v>137.19642316159391</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0.70418667691594072</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1.887293482935781</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>5.6912533077739689E-3</v>
+      </c>
+      <c r="M38" s="4">
+        <v>4.6304605019355076</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>13</v>
       </c>
-      <c r="B38">
-        <v>4</v>
-      </c>
-      <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="F38">
-        <v>3</v>
-      </c>
-      <c r="G38">
-        <v>137.1964231615939</v>
-      </c>
-      <c r="H38">
-        <v>0.246176729810117</v>
-      </c>
-      <c r="I38">
-        <v>37.26484840464092</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0.005691253307773969</v>
-      </c>
-      <c r="M38">
-        <v>2.465466819759329</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
       <c r="B39">
         <v>5</v>
       </c>
@@ -2000,13 +2040,13 @@
         <v>5</v>
       </c>
       <c r="G39">
-        <v>159.1056412237108</v>
-      </c>
-      <c r="H39">
-        <v>0.4786662476055216</v>
-      </c>
-      <c r="I39">
-        <v>63.75983271111421</v>
+        <v>159.10564122371079</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0.8194846209485811</v>
+      </c>
+      <c r="I39" s="2">
+        <v>4.162476458805302</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2015,98 +2055,98 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0.006479433927828825</v>
-      </c>
-      <c r="M39">
-        <v>3.097227281245376</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>6.4794339278288248E-3</v>
+      </c>
+      <c r="M39" s="4">
+        <v>3.529589725156804</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>4</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40">
+        <v>153.89266321297461</v>
+      </c>
+      <c r="H40" s="6">
+        <v>1.1033793043424169</v>
+      </c>
+      <c r="I40" s="2">
+        <v>4.371347510326788</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>8.1259384733811425E-3</v>
+      </c>
+      <c r="M40" s="4">
+        <v>3.595454721171286</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>3</v>
+      </c>
+      <c r="C41">
+        <v>4</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>133.79823141773451</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0.59228392089151116</v>
+      </c>
+      <c r="I41" s="2">
+        <v>4.7705238200132101</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>5</v>
+      </c>
+      <c r="L41">
+        <v>9.4839411960197118E-3</v>
+      </c>
+      <c r="M41" s="4">
+        <v>4.0950331552699701</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>13</v>
       </c>
-      <c r="B40">
-        <v>4</v>
-      </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40">
-        <v>3</v>
-      </c>
-      <c r="E40">
-        <v>4</v>
-      </c>
-      <c r="F40">
-        <v>3</v>
-      </c>
-      <c r="G40">
-        <v>153.8926632129746</v>
-      </c>
-      <c r="H40">
-        <v>0.4027533312376105</v>
-      </c>
-      <c r="I40">
-        <v>33.21718911417031</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-      <c r="L40">
-        <v>0.008125938473381143</v>
-      </c>
-      <c r="M40">
-        <v>2.285426933289371</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41">
-        <v>3</v>
-      </c>
-      <c r="C41">
-        <v>4</v>
-      </c>
-      <c r="D41">
-        <v>4</v>
-      </c>
-      <c r="E41">
-        <v>4</v>
-      </c>
-      <c r="F41">
-        <v>4</v>
-      </c>
-      <c r="G41">
-        <v>133.7982314177345</v>
-      </c>
-      <c r="H41">
-        <v>0.3137987363582652</v>
-      </c>
-      <c r="I41">
-        <v>51.7424487234255</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>5</v>
-      </c>
-      <c r="L41">
-        <v>0.009483941196019712</v>
-      </c>
-      <c r="M41">
-        <v>2.37427104923015</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
       <c r="B42">
         <v>5</v>
       </c>
@@ -2123,13 +2163,13 @@
         <v>4</v>
       </c>
       <c r="G42">
-        <v>152.7975734978671</v>
-      </c>
-      <c r="H42">
-        <v>0.2129522577770149</v>
-      </c>
-      <c r="I42">
-        <v>65.41380723057001</v>
+        <v>152.79757349786709</v>
+      </c>
+      <c r="H42" s="6">
+        <v>0.95686498365103234</v>
+      </c>
+      <c r="I42" s="2">
+        <v>4.5419630165294649</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -2138,15 +2178,15 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0.004693283600678183</v>
-      </c>
-      <c r="M42">
-        <v>2.472171654282024</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>4.6932836006781829E-3</v>
+      </c>
+      <c r="M42" s="4">
+        <v>4.5168566185079237</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B43">
         <v>4</v>
@@ -2166,11 +2206,11 @@
       <c r="G43">
         <v>144.0161399855489</v>
       </c>
-      <c r="H43">
-        <v>0.1901624008138808</v>
-      </c>
-      <c r="I43">
-        <v>24.33439622228822</v>
+      <c r="H43" s="6">
+        <v>1.226785688570607</v>
+      </c>
+      <c r="I43" s="2">
+        <v>5.2766586254296293</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2179,15 +2219,15 @@
         <v>2</v>
       </c>
       <c r="L43">
-        <v>0.006856651926885126</v>
-      </c>
-      <c r="M43">
-        <v>2.092854444153283</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>6.856651926885126E-3</v>
+      </c>
+      <c r="M43" s="4">
+        <v>3.4635039224995419</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B44">
         <v>4</v>
@@ -2205,13 +2245,13 @@
         <v>5</v>
       </c>
       <c r="G44">
-        <v>151.6972928439037</v>
-      </c>
-      <c r="H44">
-        <v>0.3544696959572824</v>
-      </c>
-      <c r="I44">
-        <v>74.8804407937875</v>
+        <v>151.69729284390371</v>
+      </c>
+      <c r="H44" s="6">
+        <v>0.49812919135969308</v>
+      </c>
+      <c r="I44" s="2">
+        <v>4.5002429533624184</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2220,15 +2260,15 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>0.006580134095075202</v>
-      </c>
-      <c r="M44">
-        <v>2.636304297869932</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>6.5801340950752017E-3</v>
+      </c>
+      <c r="M44" s="4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -2248,11 +2288,11 @@
       <c r="G45">
         <v>103.6188595786731</v>
       </c>
-      <c r="H45">
-        <v>0.1225955642768971</v>
-      </c>
-      <c r="I45">
-        <v>34.121708368275</v>
+      <c r="H45" s="6">
+        <v>0.94615846463307607</v>
+      </c>
+      <c r="I45" s="2">
+        <v>3.6677005560575369</v>
       </c>
       <c r="J45">
         <v>6</v>
@@ -2261,15 +2301,15 @@
         <v>5</v>
       </c>
       <c r="L45">
-        <v>0.01296806057627119</v>
-      </c>
-      <c r="M45">
-        <v>1.287808502725099</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>1.296806057627119E-2</v>
+      </c>
+      <c r="M45" s="4">
+        <v>3.5778660547138932</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B46">
         <v>4</v>
@@ -2287,13 +2327,13 @@
         <v>5</v>
       </c>
       <c r="G46">
-        <v>141.251932862553</v>
-      </c>
-      <c r="H46">
-        <v>0.3299813563416223</v>
-      </c>
-      <c r="I46">
-        <v>75.09378116336106</v>
+        <v>141.25193286255299</v>
+      </c>
+      <c r="H46" s="6">
+        <v>0.96497069856210593</v>
+      </c>
+      <c r="I46" s="2">
+        <v>3.726388884208093</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2302,15 +2342,15 @@
         <v>2</v>
       </c>
       <c r="L46">
-        <v>0.006247327055231724</v>
-      </c>
-      <c r="M46">
-        <v>2.481721912541306</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>6.2473270552317241E-3</v>
+      </c>
+      <c r="M46" s="4">
+        <v>4.8233768467717022</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B47">
         <v>4</v>
@@ -2328,13 +2368,13 @@
         <v>4</v>
       </c>
       <c r="G47">
-        <v>127.7449784110866</v>
-      </c>
-      <c r="H47">
-        <v>0.2458592812235759</v>
-      </c>
-      <c r="I47">
-        <v>72.0913168392465</v>
+        <v>127.74497841108661</v>
+      </c>
+      <c r="H47" s="6">
+        <v>1.0954557179443281</v>
+      </c>
+      <c r="I47" s="2">
+        <v>3.5177788110127892</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2343,15 +2383,15 @@
         <v>2</v>
       </c>
       <c r="L47">
-        <v>0.007110311752837224</v>
-      </c>
-      <c r="M47">
-        <v>3.151706762892592</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>7.1103117528372242E-3</v>
+      </c>
+      <c r="M47" s="4">
+        <v>4.3058810306101236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B48">
         <v>4</v>
@@ -2371,11 +2411,11 @@
       <c r="G48">
         <v>154.4577547807304</v>
       </c>
-      <c r="H48">
-        <v>0.3278845958016099</v>
-      </c>
-      <c r="I48">
-        <v>66.63083985549318</v>
+      <c r="H48" s="6">
+        <v>0.59076232228047953</v>
+      </c>
+      <c r="I48" s="2">
+        <v>4.0954775244231829</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2384,15 +2424,15 @@
         <v>1</v>
       </c>
       <c r="L48">
-        <v>0.009017205899697673</v>
-      </c>
-      <c r="M48">
-        <v>2.451178261074259</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>9.0172058996976726E-3</v>
+      </c>
+      <c r="M48" s="4">
+        <v>4.8943248822723273</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B49">
         <v>3</v>
@@ -2410,13 +2450,13 @@
         <v>4</v>
       </c>
       <c r="G49">
-        <v>152.5334809752486</v>
-      </c>
-      <c r="H49">
-        <v>0.3109535189148533</v>
-      </c>
-      <c r="I49">
-        <v>52.55186914859623</v>
+        <v>152.53348097524861</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0.56988584672893094</v>
+      </c>
+      <c r="I49" s="2">
+        <v>2.702654131433341</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -2425,15 +2465,15 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0.008735698073326364</v>
-      </c>
-      <c r="M49">
-        <v>2.119045794750979</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>8.7356980733263642E-3</v>
+      </c>
+      <c r="M49" s="4">
+        <v>3.4209103147203819</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B50">
         <v>3</v>
@@ -2453,11 +2493,11 @@
       <c r="G50">
         <v>147.2151384760507</v>
       </c>
-      <c r="H50">
-        <v>0.2679107219423305</v>
-      </c>
-      <c r="I50">
-        <v>40.51430653465626</v>
+      <c r="H50" s="6">
+        <v>1.030485391404224</v>
+      </c>
+      <c r="I50" s="2">
+        <v>4.140922198558953</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2466,15 +2506,15 @@
         <v>4</v>
       </c>
       <c r="L50">
-        <v>0.007942936714271992</v>
-      </c>
-      <c r="M50">
-        <v>3.161607330521246</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>7.9429367142719916E-3</v>
+      </c>
+      <c r="M50" s="4">
+        <v>3.1163622394015662</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -2494,11 +2534,11 @@
       <c r="G51">
         <v>155.2395266710779</v>
       </c>
-      <c r="H51">
-        <v>0.380810790848403</v>
-      </c>
-      <c r="I51">
-        <v>63.69587375970366</v>
+      <c r="H51" s="6">
+        <v>0.97424616830829658</v>
+      </c>
+      <c r="I51" s="2">
+        <v>3.713586493168386</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -2507,15 +2547,15 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0.0060517834670159</v>
-      </c>
-      <c r="M51">
-        <v>2.650526449827979</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>6.0517834670158997E-3</v>
+      </c>
+      <c r="M51" s="4">
+        <v>4.3775291315885241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -2535,11 +2575,11 @@
       <c r="G52">
         <v>103.2843060141974</v>
       </c>
-      <c r="H52">
-        <v>0.3169021525289393</v>
-      </c>
-      <c r="I52">
-        <v>21.10612972954593</v>
+      <c r="H52" s="6">
+        <v>0.9626232125864691</v>
+      </c>
+      <c r="I52" s="2">
+        <v>4.0756351578874073</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2548,15 +2588,15 @@
         <v>6</v>
       </c>
       <c r="L52">
-        <v>0.005987428187527575</v>
-      </c>
-      <c r="M52">
-        <v>1.493123131781844</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>5.9874281875275754E-3</v>
+      </c>
+      <c r="M52" s="4">
+        <v>4.2440136426110273</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B53">
         <v>4</v>
@@ -2574,13 +2614,13 @@
         <v>4</v>
       </c>
       <c r="G53">
-        <v>147.7500396297218</v>
-      </c>
-      <c r="H53">
-        <v>0.2587882357563795</v>
-      </c>
-      <c r="I53">
-        <v>63.55579381966844</v>
+        <v>147.75003962972181</v>
+      </c>
+      <c r="H53" s="6">
+        <v>0.98661205237424399</v>
+      </c>
+      <c r="I53" s="2">
+        <v>4.0787230349706611</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -2589,15 +2629,15 @@
         <v>1</v>
       </c>
       <c r="L53">
-        <v>0.004274592792920042</v>
-      </c>
-      <c r="M53">
-        <v>1.826623896031793</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>4.2745927929200419E-3</v>
+      </c>
+      <c r="M53" s="4">
+        <v>4.2833325922263548</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -2617,11 +2657,11 @@
       <c r="G54">
         <v>161.3985367938067</v>
       </c>
-      <c r="H54">
-        <v>0.03928955453999784</v>
-      </c>
-      <c r="I54">
-        <v>45.82873403560432</v>
+      <c r="H54" s="6">
+        <v>0.72999381960537735</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1.3477353986842671</v>
       </c>
       <c r="J54">
         <v>3</v>
@@ -2630,15 +2670,15 @@
         <v>6</v>
       </c>
       <c r="L54">
-        <v>0.00136259457180251</v>
-      </c>
-      <c r="M54">
-        <v>2.274271357258984</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>1.36259457180251E-3</v>
+      </c>
+      <c r="M54" s="4">
+        <v>4.6597979855903402</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -2658,11 +2698,11 @@
       <c r="G55">
         <v>135.4311018998832</v>
       </c>
-      <c r="H55">
-        <v>0.1525571336409433</v>
-      </c>
-      <c r="I55">
-        <v>3.837242043913257</v>
+      <c r="H55" s="6">
+        <v>0.95806342429025093</v>
+      </c>
+      <c r="I55" s="2">
+        <v>2.8987061813353319</v>
       </c>
       <c r="J55">
         <v>5</v>
@@ -2671,15 +2711,15 @@
         <v>8</v>
       </c>
       <c r="L55">
-        <v>0.01292377582555265</v>
-      </c>
-      <c r="M55">
-        <v>1.613609677229518</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>1.2923775825552651E-2</v>
+      </c>
+      <c r="M55" s="4">
+        <v>4.3530109543473552</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B56">
         <v>3</v>
@@ -2699,11 +2739,11 @@
       <c r="G56">
         <v>144.8919953336318</v>
       </c>
-      <c r="H56">
-        <v>0.1499109138891758</v>
-      </c>
-      <c r="I56">
-        <v>61.08832423048281</v>
+      <c r="H56" s="6">
+        <v>0.97326811832467031</v>
+      </c>
+      <c r="I56" s="2">
+        <v>3.691371335911144</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2712,15 +2752,15 @@
         <v>1</v>
       </c>
       <c r="L56">
-        <v>0.006630195727114022</v>
-      </c>
-      <c r="M56">
-        <v>1.933011247942829</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>6.630195727114022E-3</v>
+      </c>
+      <c r="M56" s="4">
+        <v>4.3433705558842268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -2740,11 +2780,11 @@
       <c r="G57">
         <v>122.1201990269128</v>
       </c>
-      <c r="H57">
-        <v>0.2449716080595938</v>
-      </c>
-      <c r="I57">
-        <v>19.58518781116152</v>
+      <c r="H57" s="6">
+        <v>0.72141214549340804</v>
+      </c>
+      <c r="I57" s="2">
+        <v>3.7445150417023259</v>
       </c>
       <c r="J57">
         <v>3</v>
@@ -2753,15 +2793,15 @@
         <v>7</v>
       </c>
       <c r="L57">
-        <v>0.006566609122855393</v>
-      </c>
-      <c r="M57">
-        <v>1.712224434636181</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>6.5666091228553927E-3</v>
+      </c>
+      <c r="M57" s="4">
+        <v>4.5290042082806838</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -2779,13 +2819,13 @@
         <v>4</v>
       </c>
       <c r="G58">
-        <v>137.1155262024268</v>
-      </c>
-      <c r="H58">
-        <v>0.3550408711127026</v>
-      </c>
-      <c r="I58">
-        <v>53.70407014023672</v>
+        <v>137.11552620242679</v>
+      </c>
+      <c r="H58" s="6">
+        <v>1.3664436277861891</v>
+      </c>
+      <c r="I58" s="2">
+        <v>4.0593893089996937</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -2794,15 +2834,15 @@
         <v>1</v>
       </c>
       <c r="L58">
-        <v>0.005551863655309501</v>
-      </c>
-      <c r="M58">
-        <v>2.751205946862775</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>5.5518636553095009E-3</v>
+      </c>
+      <c r="M58" s="4">
+        <v>4.4014499793122157</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B59">
         <v>4</v>
@@ -2820,13 +2860,13 @@
         <v>4</v>
       </c>
       <c r="G59">
-        <v>159.8269098394551</v>
-      </c>
-      <c r="H59">
-        <v>0.409308909116206</v>
-      </c>
-      <c r="I59">
-        <v>72.57138130093971</v>
+        <v>159.82690983945511</v>
+      </c>
+      <c r="H59" s="6">
+        <v>1.018458230227947</v>
+      </c>
+      <c r="I59" s="2">
+        <v>4.1023482903316424</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -2835,15 +2875,15 @@
         <v>1</v>
       </c>
       <c r="L59">
-        <v>0.005371593830486527</v>
-      </c>
-      <c r="M59">
-        <v>2.676320419890754</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>5.3715938304865268E-3</v>
+      </c>
+      <c r="M59" s="4">
+        <v>4.6144675590304427</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B60">
         <v>4</v>
@@ -2861,13 +2901,13 @@
         <v>4</v>
       </c>
       <c r="G60">
-        <v>143.8848219700805</v>
-      </c>
-      <c r="H60">
-        <v>0.2796669451575888</v>
-      </c>
-      <c r="I60">
-        <v>60.76766753889096</v>
+        <v>143.88482197008051</v>
+      </c>
+      <c r="H60" s="6">
+        <v>0.60217412569933781</v>
+      </c>
+      <c r="I60" s="2">
+        <v>5.3162333229338961</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -2876,15 +2916,15 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0.003648315394383666</v>
-      </c>
-      <c r="M60">
-        <v>2.510120222233612</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>3.648315394383666E-3</v>
+      </c>
+      <c r="M60" s="4">
+        <v>4.7051124948671488</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B61">
         <v>3</v>
@@ -2904,11 +2944,11 @@
       <c r="G61">
         <v>179.4857309725609</v>
       </c>
-      <c r="H61">
-        <v>0.1096170527539813</v>
-      </c>
-      <c r="I61">
-        <v>48.51327225511329</v>
+      <c r="H61" s="6">
+        <v>1.064138402158457</v>
+      </c>
+      <c r="I61" s="2">
+        <v>4.1124584810979474</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -2917,15 +2957,15 @@
         <v>3</v>
       </c>
       <c r="L61">
-        <v>0.006039754820407413</v>
-      </c>
-      <c r="M61">
-        <v>3.08954065852045</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>6.0397548204074126E-3</v>
+      </c>
+      <c r="M61" s="4">
+        <v>5.0190132807445487</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B62">
         <v>3</v>
@@ -2945,11 +2985,11 @@
       <c r="G62">
         <v>169.6254103044617</v>
       </c>
-      <c r="H62">
-        <v>0.2462188277896793</v>
-      </c>
-      <c r="I62">
-        <v>31.30457218787998</v>
+      <c r="H62" s="6">
+        <v>0.65632958244316963</v>
+      </c>
+      <c r="I62" s="2">
+        <v>3.4869762917835589</v>
       </c>
       <c r="J62">
         <v>3</v>
@@ -2958,15 +2998,15 @@
         <v>2</v>
       </c>
       <c r="L62">
-        <v>0.006199237279633364</v>
-      </c>
-      <c r="M62">
-        <v>2.377669971269986</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>6.199237279633364E-3</v>
+      </c>
+      <c r="M62" s="4">
+        <v>3.7104852050577919</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B63">
         <v>4</v>
@@ -2984,13 +3024,13 @@
         <v>5</v>
       </c>
       <c r="G63">
-        <v>156.2067209755068</v>
-      </c>
-      <c r="H63">
-        <v>0.3845810340475433</v>
-      </c>
-      <c r="I63">
-        <v>82.86148455106442</v>
+        <v>156.20672097550681</v>
+      </c>
+      <c r="H63" s="6">
+        <v>1.0967711509356131</v>
+      </c>
+      <c r="I63" s="2">
+        <v>2.2008765274625168</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -2999,15 +3039,15 @@
         <v>2</v>
       </c>
       <c r="L63">
-        <v>0.00635484517237325</v>
-      </c>
-      <c r="M63">
-        <v>2.905728526060613</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>6.3548451723732498E-3</v>
+      </c>
+      <c r="M63" s="4">
+        <v>4.3883372644464478</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64">
         <v>2</v>
@@ -3027,11 +3067,11 @@
       <c r="G64">
         <v>118.5923643826517</v>
       </c>
-      <c r="H64">
-        <v>0.1707687687163111</v>
-      </c>
-      <c r="I64">
-        <v>29.0736825579306</v>
+      <c r="H64" s="6">
+        <v>1.1896488947518511</v>
+      </c>
+      <c r="I64" s="2">
+        <v>2.4314098844581431</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -3040,57 +3080,57 @@
         <v>10</v>
       </c>
       <c r="L64">
-        <v>0.006893005696718762</v>
-      </c>
-      <c r="M64">
-        <v>1.337936031054216</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+        <v>6.8930056967187623E-3</v>
+      </c>
+      <c r="M64" s="4">
+        <v>3.877805978841621</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65">
+        <v>4</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+      <c r="F65">
+        <v>4</v>
+      </c>
+      <c r="G65">
+        <v>147.51550015276021</v>
+      </c>
+      <c r="H65" s="6">
+        <v>0.69482942041207241</v>
+      </c>
+      <c r="I65" s="2">
+        <v>4.3354918099752036</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65">
+        <v>4</v>
+      </c>
+      <c r="L65">
+        <v>9.0202739984508885E-3</v>
+      </c>
+      <c r="M65" s="4">
+        <v>3.5998646076324401</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
         <v>13</v>
       </c>
-      <c r="B65">
-        <v>4</v>
-      </c>
-      <c r="C65">
-        <v>3</v>
-      </c>
-      <c r="D65">
-        <v>3</v>
-      </c>
-      <c r="E65">
-        <v>4</v>
-      </c>
-      <c r="F65">
-        <v>4</v>
-      </c>
-      <c r="G65">
-        <v>147.5155001527602</v>
-      </c>
-      <c r="H65">
-        <v>0.04765300480602719</v>
-      </c>
-      <c r="I65">
-        <v>65.57813249401636</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>4</v>
-      </c>
-      <c r="L65">
-        <v>0.009020273998450888</v>
-      </c>
-      <c r="M65">
-        <v>2.341121640217113</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
       <c r="B66">
         <v>4</v>
       </c>
@@ -3107,13 +3147,13 @@
         <v>4</v>
       </c>
       <c r="G66">
-        <v>157.1339959020545</v>
-      </c>
-      <c r="H66">
-        <v>0.3523508606561873</v>
-      </c>
-      <c r="I66">
-        <v>82.23170950591458</v>
+        <v>157.13399590205449</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1.14084403231108</v>
+      </c>
+      <c r="I66" s="2">
+        <v>4.8604468141104684</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -3122,56 +3162,56 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>0.004316568209869877</v>
-      </c>
-      <c r="M66">
-        <v>2.883965502029533</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>4.3165682098698773E-3</v>
+      </c>
+      <c r="M66" s="4">
+        <v>3.6862758073517798</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>144.70792945205201</v>
+      </c>
+      <c r="H67" s="6">
+        <v>1.0031952317341251</v>
+      </c>
+      <c r="I67" s="2">
+        <v>5.3413709969181822</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>2</v>
+      </c>
+      <c r="L67">
+        <v>8.3344121870636764E-3</v>
+      </c>
+      <c r="M67" s="4">
+        <v>4.3969733105369153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
         <v>13</v>
-      </c>
-      <c r="B67">
-        <v>4</v>
-      </c>
-      <c r="C67">
-        <v>3</v>
-      </c>
-      <c r="D67">
-        <v>3</v>
-      </c>
-      <c r="E67">
-        <v>4</v>
-      </c>
-      <c r="F67">
-        <v>3</v>
-      </c>
-      <c r="G67">
-        <v>144.707929452052</v>
-      </c>
-      <c r="H67">
-        <v>0.2729579166763147</v>
-      </c>
-      <c r="I67">
-        <v>24.97738827721474</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
-      </c>
-      <c r="K67">
-        <v>2</v>
-      </c>
-      <c r="L67">
-        <v>0.008334412187063676</v>
-      </c>
-      <c r="M67">
-        <v>2.884190946218233</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
-      <c r="A68" t="s">
-        <v>15</v>
       </c>
       <c r="B68">
         <v>4</v>
@@ -3191,11 +3231,11 @@
       <c r="G68">
         <v>130.6632169889244</v>
       </c>
-      <c r="H68">
-        <v>0.2896302084176813</v>
-      </c>
-      <c r="I68">
-        <v>59.29421920322832</v>
+      <c r="H68" s="6">
+        <v>1.105515039998622</v>
+      </c>
+      <c r="I68" s="2">
+        <v>2.9721069210842872</v>
       </c>
       <c r="J68">
         <v>2</v>
@@ -3204,15 +3244,15 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>0.005682623236457147</v>
-      </c>
-      <c r="M68">
-        <v>3.161944551081238</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
+        <v>5.6826232364571468E-3</v>
+      </c>
+      <c r="M68" s="4">
+        <v>4.3509515328716004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -3230,13 +3270,13 @@
         <v>2</v>
       </c>
       <c r="G69">
-        <v>96.72206172906668</v>
-      </c>
-      <c r="H69">
-        <v>0.2638170740137805</v>
-      </c>
-      <c r="I69">
-        <v>20.02620063605262</v>
+        <v>96.722061729066681</v>
+      </c>
+      <c r="H69" s="6">
+        <v>1.3741982456634869</v>
+      </c>
+      <c r="I69" s="2">
+        <v>3.496135564569073</v>
       </c>
       <c r="J69">
         <v>2</v>
@@ -3245,15 +3285,15 @@
         <v>2</v>
       </c>
       <c r="L69">
-        <v>0.01406109141194706</v>
-      </c>
-      <c r="M69">
-        <v>2.377672785020427</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
+        <v>1.4061091411947059E-2</v>
+      </c>
+      <c r="M69" s="4">
+        <v>4.3402472175430624</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B70">
         <v>5</v>
@@ -3271,13 +3311,13 @@
         <v>4</v>
       </c>
       <c r="G70">
-        <v>164.2050424798985</v>
-      </c>
-      <c r="H70">
-        <v>0.3214626853125261</v>
-      </c>
-      <c r="I70">
-        <v>61.67644426895771</v>
+        <v>164.20504247989851</v>
+      </c>
+      <c r="H70" s="6">
+        <v>0.83865297099928238</v>
+      </c>
+      <c r="I70" s="2">
+        <v>4.0423336860831123</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3286,15 +3326,15 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>0.005471415556386404</v>
-      </c>
-      <c r="M70">
-        <v>3.171475273006542</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
+        <v>5.4714155563864043E-3</v>
+      </c>
+      <c r="M70" s="4">
+        <v>3.9645718114583999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -3312,13 +3352,13 @@
         <v>2</v>
       </c>
       <c r="G71">
-        <v>128.7567660313329</v>
-      </c>
-      <c r="H71">
-        <v>0.0006170358785759222</v>
-      </c>
-      <c r="I71">
-        <v>14.25915818899008</v>
+        <v>128.75676603133289</v>
+      </c>
+      <c r="H71" s="6">
+        <v>0.71156595891062757</v>
+      </c>
+      <c r="I71" s="2">
+        <v>5.847398921130238</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3327,15 +3367,15 @@
         <v>5</v>
       </c>
       <c r="L71">
-        <v>0.01105817311118122</v>
-      </c>
-      <c r="M71">
-        <v>1.940851568348413</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
+        <v>1.105817311118122E-2</v>
+      </c>
+      <c r="M71" s="4">
+        <v>4.1020488507070461</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B72">
         <v>3</v>
@@ -3355,11 +3395,11 @@
       <c r="G72">
         <v>132.2358305144574</v>
       </c>
-      <c r="H72">
-        <v>0.2679030361311119</v>
-      </c>
-      <c r="I72">
-        <v>49.80292524712698</v>
+      <c r="H72" s="6">
+        <v>0.6776213925936192</v>
+      </c>
+      <c r="I72" s="2">
+        <v>3.9148614682138949</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3368,15 +3408,15 @@
         <v>3</v>
       </c>
       <c r="L72">
-        <v>0.009376786546896169</v>
-      </c>
-      <c r="M72">
-        <v>2.575178455597789</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+        <v>9.3767865468961688E-3</v>
+      </c>
+      <c r="M72" s="4">
+        <v>4.5906516175256291</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B73">
         <v>4</v>
@@ -3394,13 +3434,13 @@
         <v>4</v>
       </c>
       <c r="G73">
-        <v>146.4070790921294</v>
-      </c>
-      <c r="H73">
-        <v>0.3366881233919271</v>
-      </c>
-      <c r="I73">
-        <v>67.31363941612697</v>
+        <v>146.40707909212941</v>
+      </c>
+      <c r="H73" s="6">
+        <v>0.69604742875864045</v>
+      </c>
+      <c r="I73" s="2">
+        <v>5.3512628547329708</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -3409,15 +3449,15 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>0.004071730548583549</v>
-      </c>
-      <c r="M73">
-        <v>2.818873761784634</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
+        <v>4.0717305485835492E-3</v>
+      </c>
+      <c r="M73" s="4">
+        <v>3.2063641642104161</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B74">
         <v>4</v>
@@ -3437,11 +3477,11 @@
       <c r="G74">
         <v>146.296766314027</v>
       </c>
-      <c r="H74">
-        <v>0.3083220506360366</v>
-      </c>
-      <c r="I74">
-        <v>63.10459678919634</v>
+      <c r="H74" s="6">
+        <v>0.88072457264647397</v>
+      </c>
+      <c r="I74" s="2">
+        <v>3.9699729029073079</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3450,15 +3490,15 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0.005494955517561526</v>
-      </c>
-      <c r="M74">
-        <v>2.738219813603981</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
+        <v>5.4949555175615259E-3</v>
+      </c>
+      <c r="M74" s="4">
+        <v>4.1147852590571503</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -3478,11 +3518,11 @@
       <c r="G75">
         <v>110.928730963123</v>
       </c>
-      <c r="H75">
-        <v>0.1109061430334775</v>
-      </c>
-      <c r="I75">
-        <v>14.94352649430611</v>
+      <c r="H75" s="6">
+        <v>0.98528799370416098</v>
+      </c>
+      <c r="I75" s="2">
+        <v>4.9532451864284557</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -3491,15 +3531,15 @@
         <v>6</v>
       </c>
       <c r="L75">
-        <v>0.01396167828681107</v>
-      </c>
-      <c r="M75">
-        <v>1.658487904375172</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
+        <v>1.396167828681107E-2</v>
+      </c>
+      <c r="M75" s="4">
+        <v>4.1539736888760732</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B76">
         <v>3</v>
@@ -3517,13 +3557,13 @@
         <v>4</v>
       </c>
       <c r="G76">
-        <v>132.7980219845622</v>
-      </c>
-      <c r="H76">
-        <v>0.2602242157893426</v>
-      </c>
-      <c r="I76">
-        <v>54.40522720145681</v>
+        <v>132.79802198456221</v>
+      </c>
+      <c r="H76" s="6">
+        <v>0.96917269983250476</v>
+      </c>
+      <c r="I76" s="2">
+        <v>4.8265798465520779</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -3532,15 +3572,15 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>0.005948389225374087</v>
-      </c>
-      <c r="M76">
-        <v>2.360688477900301</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
+        <v>5.9483892253740867E-3</v>
+      </c>
+      <c r="M76" s="4">
+        <v>4.5519825614465894</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B77">
         <v>4</v>
@@ -3560,11 +3600,11 @@
       <c r="G77">
         <v>109.4713963906174</v>
       </c>
-      <c r="H77">
-        <v>0.2409606574505531</v>
-      </c>
-      <c r="I77">
-        <v>35.30077939773257</v>
+      <c r="H77" s="6">
+        <v>1.106795812259006</v>
+      </c>
+      <c r="I77" s="2">
+        <v>3.9660881325081512</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3573,56 +3613,56 @@
         <v>3</v>
       </c>
       <c r="L77">
-        <v>0.007927447714780864</v>
-      </c>
-      <c r="M77">
-        <v>2.573345067264342</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
+        <v>7.9274477147808636E-3</v>
+      </c>
+      <c r="M77" s="4">
+        <v>3.2898509528343052</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78">
+        <v>3</v>
+      </c>
+      <c r="C78">
+        <v>4</v>
+      </c>
+      <c r="D78">
+        <v>4</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78">
+        <v>149.75301766937989</v>
+      </c>
+      <c r="H78" s="6">
+        <v>0.9032504729694768</v>
+      </c>
+      <c r="I78" s="2">
+        <v>2.7796167527378448</v>
+      </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
+      <c r="K78">
+        <v>3</v>
+      </c>
+      <c r="L78">
+        <v>4.8598304673476951E-3</v>
+      </c>
+      <c r="M78" s="4">
+        <v>4.9970802473104463</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>13</v>
-      </c>
-      <c r="B78">
-        <v>3</v>
-      </c>
-      <c r="C78">
-        <v>4</v>
-      </c>
-      <c r="D78">
-        <v>4</v>
-      </c>
-      <c r="E78">
-        <v>3</v>
-      </c>
-      <c r="F78">
-        <v>4</v>
-      </c>
-      <c r="G78">
-        <v>149.7530176693799</v>
-      </c>
-      <c r="H78">
-        <v>0.2420659308976494</v>
-      </c>
-      <c r="I78">
-        <v>72.159643952572</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78">
-        <v>3</v>
-      </c>
-      <c r="L78">
-        <v>0.004859830467347695</v>
-      </c>
-      <c r="M78">
-        <v>2.024538172742867</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
-      <c r="A79" t="s">
-        <v>15</v>
       </c>
       <c r="B79">
         <v>4</v>
@@ -3642,11 +3682,11 @@
       <c r="G79">
         <v>164.4376460407326</v>
       </c>
-      <c r="H79">
-        <v>0.3290539940375726</v>
-      </c>
-      <c r="I79">
-        <v>65.18226737015161</v>
+      <c r="H79" s="6">
+        <v>1.263383519289329</v>
+      </c>
+      <c r="I79" s="2">
+        <v>3.530905562071049</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -3655,56 +3695,56 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>0.006626519471699682</v>
-      </c>
-      <c r="M79">
-        <v>2.20374100268696</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
+        <v>6.6265194716996819E-3</v>
+      </c>
+      <c r="M79" s="4">
+        <v>4.2281782546571058</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80">
+        <v>3</v>
+      </c>
+      <c r="E80">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <v>4</v>
+      </c>
+      <c r="G80">
+        <v>158.73802651231301</v>
+      </c>
+      <c r="H80" s="6">
+        <v>0.83383579169051103</v>
+      </c>
+      <c r="I80" s="2">
+        <v>5.289045173884479</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+      <c r="L80">
+        <v>6.9004669807018306E-3</v>
+      </c>
+      <c r="M80" s="4">
+        <v>4.2599483280169617</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>13</v>
-      </c>
-      <c r="B80">
-        <v>4</v>
-      </c>
-      <c r="C80">
-        <v>3</v>
-      </c>
-      <c r="D80">
-        <v>3</v>
-      </c>
-      <c r="E80">
-        <v>4</v>
-      </c>
-      <c r="F80">
-        <v>4</v>
-      </c>
-      <c r="G80">
-        <v>158.738026512313</v>
-      </c>
-      <c r="H80">
-        <v>0.2893123653615598</v>
-      </c>
-      <c r="I80">
-        <v>37.63138996638172</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
-        <v>2</v>
-      </c>
-      <c r="L80">
-        <v>0.006900466980701831</v>
-      </c>
-      <c r="M80">
-        <v>2.177750277609689</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
-      <c r="A81" t="s">
-        <v>15</v>
       </c>
       <c r="B81">
         <v>4</v>
@@ -3724,11 +3764,11 @@
       <c r="G81">
         <v>149.8571096861003</v>
       </c>
-      <c r="H81">
-        <v>0.3648229466999279</v>
-      </c>
-      <c r="I81">
-        <v>69.59142066403992</v>
+      <c r="H81" s="6">
+        <v>1.5800422916474051</v>
+      </c>
+      <c r="I81" s="2">
+        <v>4.6778251684801138</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -3737,15 +3777,15 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>0.004062977995600074</v>
-      </c>
-      <c r="M81">
-        <v>3.02376040500412</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
+        <v>4.0629779956000743E-3</v>
+      </c>
+      <c r="M81" s="4">
+        <v>3.859172145600664</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -3765,11 +3805,11 @@
       <c r="G82">
         <v>125.7160031730166</v>
       </c>
-      <c r="H82">
-        <v>0.1925457561784965</v>
-      </c>
-      <c r="I82">
-        <v>10.4953578530618</v>
+      <c r="H82" s="6">
+        <v>1.0564168369412521</v>
+      </c>
+      <c r="I82" s="2">
+        <v>3.3663496732281528</v>
       </c>
       <c r="J82">
         <v>2</v>
@@ -3778,15 +3818,15 @@
         <v>4</v>
       </c>
       <c r="L82">
-        <v>0.01180915457543208</v>
-      </c>
-      <c r="M82">
-        <v>1.983353123179021</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13">
+        <v>1.1809154575432079E-2</v>
+      </c>
+      <c r="M82" s="4">
+        <v>4.4228134128781056</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B83">
         <v>4</v>
@@ -3804,13 +3844,13 @@
         <v>3</v>
       </c>
       <c r="G83">
-        <v>109.3739769736356</v>
-      </c>
-      <c r="H83">
-        <v>0.212311346215784</v>
-      </c>
-      <c r="I83">
-        <v>62.90149130260747</v>
+        <v>109.37397697363561</v>
+      </c>
+      <c r="H83" s="6">
+        <v>0.68571061089592944</v>
+      </c>
+      <c r="I83" s="2">
+        <v>3.4576913613756011</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -3819,15 +3859,15 @@
         <v>3</v>
       </c>
       <c r="L83">
-        <v>0.007203528145975251</v>
-      </c>
-      <c r="M83">
-        <v>2.317790455725616</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
+        <v>7.2035281459752508E-3</v>
+      </c>
+      <c r="M83" s="4">
+        <v>4.128772430169863</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B84">
         <v>4</v>
@@ -3847,11 +3887,11 @@
       <c r="G84">
         <v>140.8944555488026</v>
       </c>
-      <c r="H84">
-        <v>0.1982450577835541</v>
-      </c>
-      <c r="I84">
-        <v>58.37867976336308</v>
+      <c r="H84" s="6">
+        <v>0.63227687548472189</v>
+      </c>
+      <c r="I84" s="2">
+        <v>2.0691268962344318</v>
       </c>
       <c r="J84">
         <v>2</v>
@@ -3860,15 +3900,15 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>0.007786970770843499</v>
-      </c>
-      <c r="M84">
-        <v>2.434360009864639</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13">
+        <v>7.7869707708434991E-3</v>
+      </c>
+      <c r="M84" s="4">
+        <v>4.8253891664638786</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B85">
         <v>5</v>
@@ -3886,13 +3926,13 @@
         <v>4</v>
       </c>
       <c r="G85">
-        <v>159.5014547099883</v>
-      </c>
-      <c r="H85">
-        <v>0.4342824150709582</v>
-      </c>
-      <c r="I85">
-        <v>65.39704555806154</v>
+        <v>159.50145470998831</v>
+      </c>
+      <c r="H85" s="6">
+        <v>1.020618103810796</v>
+      </c>
+      <c r="I85" s="2">
+        <v>5.2443387919818107</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -3901,15 +3941,15 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>0.003442417214138266</v>
-      </c>
-      <c r="M85">
-        <v>2.910872709677441</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
+        <v>3.4424172141382658E-3</v>
+      </c>
+      <c r="M85" s="4">
+        <v>3.2351034511618311</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -3927,13 +3967,13 @@
         <v>4</v>
       </c>
       <c r="G86">
-        <v>149.2802982177186</v>
-      </c>
-      <c r="H86">
-        <v>0.3403459550031601</v>
-      </c>
-      <c r="I86">
-        <v>85.58012422064867</v>
+        <v>149.28029821771861</v>
+      </c>
+      <c r="H86" s="6">
+        <v>0.84413430366853726</v>
+      </c>
+      <c r="I86" s="2">
+        <v>4.6860635602461533</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -3942,15 +3982,15 @@
         <v>3</v>
       </c>
       <c r="L86">
-        <v>0.006806742186753558</v>
-      </c>
-      <c r="M86">
-        <v>2.249323285141763</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
+        <v>6.8067421867535581E-3</v>
+      </c>
+      <c r="M86" s="4">
+        <v>4.205327497934304</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B87">
         <v>4</v>
@@ -3970,11 +4010,11 @@
       <c r="G87">
         <v>143.1739245557059</v>
       </c>
-      <c r="H87">
-        <v>0.3405002232318191</v>
-      </c>
-      <c r="I87">
-        <v>46.70303005790699</v>
+      <c r="H87" s="6">
+        <v>1.0785001235230229</v>
+      </c>
+      <c r="I87" s="2">
+        <v>3.662922178958147</v>
       </c>
       <c r="J87">
         <v>2</v>
@@ -3983,15 +4023,15 @@
         <v>3</v>
       </c>
       <c r="L87">
-        <v>0.006834298170388216</v>
-      </c>
-      <c r="M87">
-        <v>2.288050445336041</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13">
+        <v>6.8342981703882156E-3</v>
+      </c>
+      <c r="M87" s="4">
+        <v>4.345107409026455</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -4011,11 +4051,11 @@
       <c r="G88">
         <v>115.5057157918702</v>
       </c>
-      <c r="H88">
-        <v>0.2041785260361179</v>
-      </c>
-      <c r="I88">
-        <v>59.60597890119167</v>
+      <c r="H88" s="6">
+        <v>1.0183094061433859</v>
+      </c>
+      <c r="I88" s="2">
+        <v>4.0001344191734223</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -4024,15 +4064,15 @@
         <v>3</v>
       </c>
       <c r="L88">
-        <v>0.007358549208853368</v>
-      </c>
-      <c r="M88">
-        <v>2.548209055884822</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13">
+        <v>7.3585492088533676E-3</v>
+      </c>
+      <c r="M88" s="4">
+        <v>3.9881765633821451</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B89">
         <v>3</v>
@@ -4052,11 +4092,11 @@
       <c r="G89">
         <v>143.9101064873586</v>
       </c>
-      <c r="H89">
-        <v>0.04121265656136797</v>
-      </c>
-      <c r="I89">
-        <v>54.542826417139</v>
+      <c r="H89" s="6">
+        <v>0.88179277183578186</v>
+      </c>
+      <c r="I89" s="2">
+        <v>1.62913417186959</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -4065,15 +4105,15 @@
         <v>1</v>
       </c>
       <c r="L89">
-        <v>0.01022013493738676</v>
-      </c>
-      <c r="M89">
-        <v>1.906267041145405</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13">
+        <v>1.0220134937386761E-2</v>
+      </c>
+      <c r="M89" s="4">
+        <v>3.8572005060157721</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -4093,11 +4133,11 @@
       <c r="G90">
         <v>102.7511811719374</v>
       </c>
-      <c r="H90">
-        <v>0.0380330105373856</v>
-      </c>
-      <c r="I90">
-        <v>5.579777864186415</v>
+      <c r="H90" s="6">
+        <v>0.68830157048289875</v>
+      </c>
+      <c r="I90" s="2">
+        <v>3.3132855039572511</v>
       </c>
       <c r="J90">
         <v>3</v>
@@ -4106,15 +4146,15 @@
         <v>2</v>
       </c>
       <c r="L90">
-        <v>0.01664330714951408</v>
-      </c>
-      <c r="M90">
-        <v>1.061936990928006</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13">
+        <v>1.6643307149514081E-2</v>
+      </c>
+      <c r="M90" s="4">
+        <v>3.8822256326187752</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B91">
         <v>3</v>
@@ -4134,11 +4174,11 @@
       <c r="G91">
         <v>143.812608383693</v>
       </c>
-      <c r="H91">
-        <v>0.2970210388226999</v>
-      </c>
-      <c r="I91">
-        <v>51.381821588295</v>
+      <c r="H91" s="6">
+        <v>0.52128819382853386</v>
+      </c>
+      <c r="I91" s="2">
+        <v>5.1344456408641346</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -4147,15 +4187,15 @@
         <v>2</v>
       </c>
       <c r="L91">
-        <v>0.008007631391179109</v>
-      </c>
-      <c r="M91">
-        <v>1.753836226586528</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13">
+        <v>8.0076313911791094E-3</v>
+      </c>
+      <c r="M91" s="4">
+        <v>4.2047835616206974</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B92">
         <v>4</v>
@@ -4175,11 +4215,11 @@
       <c r="G92">
         <v>160.3028345403184</v>
       </c>
-      <c r="H92">
-        <v>0.3619394579513256</v>
-      </c>
-      <c r="I92">
-        <v>67.40957854179297</v>
+      <c r="H92" s="6">
+        <v>0.78837126198324481</v>
+      </c>
+      <c r="I92" s="2">
+        <v>4.7815473767300807</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -4188,15 +4228,15 @@
         <v>0</v>
       </c>
       <c r="L92">
-        <v>0.004803650150915021</v>
-      </c>
-      <c r="M92">
-        <v>2.845525908727396</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13">
+        <v>4.8036501509150214E-3</v>
+      </c>
+      <c r="M92" s="4">
+        <v>3.014024659411576</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B93">
         <v>3</v>
@@ -4214,13 +4254,13 @@
         <v>4</v>
       </c>
       <c r="G93">
-        <v>140.7791882871095</v>
-      </c>
-      <c r="H93">
-        <v>0.2652750200618653</v>
-      </c>
-      <c r="I93">
-        <v>39.26524121103459</v>
+        <v>140.77918828710949</v>
+      </c>
+      <c r="H93" s="6">
+        <v>1.114099698580868</v>
+      </c>
+      <c r="I93" s="2">
+        <v>4.1307005570639319</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -4229,15 +4269,15 @@
         <v>2</v>
       </c>
       <c r="L93">
-        <v>0.003911071012787065</v>
-      </c>
-      <c r="M93">
-        <v>2.551028724780563</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13">
+        <v>3.9110710127870651E-3</v>
+      </c>
+      <c r="M93" s="4">
+        <v>4.6790089766379372</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B94">
         <v>4</v>
@@ -4257,11 +4297,11 @@
       <c r="G94">
         <v>156.6227422510627</v>
       </c>
-      <c r="H94">
-        <v>0.1668075258299575</v>
-      </c>
-      <c r="I94">
-        <v>57.35328686075083</v>
+      <c r="H94" s="6">
+        <v>0.95352343603255096</v>
+      </c>
+      <c r="I94" s="2">
+        <v>3.785281741365063</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -4270,15 +4310,15 @@
         <v>3</v>
       </c>
       <c r="L94">
-        <v>0.004893168873652688</v>
-      </c>
-      <c r="M94">
-        <v>2.661020319206626</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13">
+        <v>4.8931688736526882E-3</v>
+      </c>
+      <c r="M94" s="4">
+        <v>3.8119208793824888</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B95">
         <v>4</v>
@@ -4298,11 +4338,11 @@
       <c r="G95">
         <v>147.4352283195891</v>
       </c>
-      <c r="H95">
-        <v>0.3034774503623289</v>
-      </c>
-      <c r="I95">
-        <v>43.7972376453226</v>
+      <c r="H95" s="6">
+        <v>0.58856530532200302</v>
+      </c>
+      <c r="I95" s="2">
+        <v>4.5964054296963264</v>
       </c>
       <c r="J95">
         <v>2</v>
@@ -4311,15 +4351,15 @@
         <v>6</v>
       </c>
       <c r="L95">
-        <v>0.005019947527387477</v>
-      </c>
-      <c r="M95">
-        <v>2.267997782701379</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13">
+        <v>5.0199475273874769E-3</v>
+      </c>
+      <c r="M95" s="4">
+        <v>4.1766816184200692</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B96">
         <v>3</v>
@@ -4339,11 +4379,11 @@
       <c r="G96">
         <v>155.0771385991703</v>
       </c>
-      <c r="H96">
-        <v>0.229809596522844</v>
-      </c>
-      <c r="I96">
-        <v>54.0872002291983</v>
+      <c r="H96" s="6">
+        <v>0.94329523146279548</v>
+      </c>
+      <c r="I96" s="2">
+        <v>3.518614893448913</v>
       </c>
       <c r="J96">
         <v>2</v>
@@ -4352,15 +4392,15 @@
         <v>3</v>
       </c>
       <c r="L96">
-        <v>0.009870363098380103</v>
-      </c>
-      <c r="M96">
-        <v>2.310730948992002</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13">
+        <v>9.8703630983801027E-3</v>
+      </c>
+      <c r="M96" s="4">
+        <v>4.3202613600728403</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B97">
         <v>4</v>
@@ -4378,13 +4418,13 @@
         <v>4</v>
       </c>
       <c r="G97">
-        <v>160.6356021996743</v>
-      </c>
-      <c r="H97">
-        <v>0.1427577117293986</v>
-      </c>
-      <c r="I97">
-        <v>63.97321575191489</v>
+        <v>160.63560219967431</v>
+      </c>
+      <c r="H97" s="6">
+        <v>0.99632934493220926</v>
+      </c>
+      <c r="I97" s="2">
+        <v>2.1353068038049918</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -4393,15 +4433,15 @@
         <v>2</v>
       </c>
       <c r="L97">
-        <v>0.002697540764258661</v>
-      </c>
-      <c r="M97">
-        <v>2.930489492519031</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13">
+        <v>2.6975407642586611E-3</v>
+      </c>
+      <c r="M97" s="4">
+        <v>3.7845167676122262</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B98">
         <v>4</v>
@@ -4419,13 +4459,13 @@
         <v>4</v>
       </c>
       <c r="G98">
-        <v>156.3449729752469</v>
-      </c>
-      <c r="H98">
-        <v>0.3727182496679654</v>
-      </c>
-      <c r="I98">
-        <v>23.01085126332873</v>
+        <v>156.34497297524689</v>
+      </c>
+      <c r="H98" s="6">
+        <v>0.6790356409497168</v>
+      </c>
+      <c r="I98" s="2">
+        <v>3.7938008603261268</v>
       </c>
       <c r="J98">
         <v>2</v>
@@ -4434,15 +4474,15 @@
         <v>0</v>
       </c>
       <c r="L98">
-        <v>0.005634015339297755</v>
-      </c>
-      <c r="M98">
-        <v>2.052976732484415</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13">
+        <v>5.6340153392977549E-3</v>
+      </c>
+      <c r="M98" s="4">
+        <v>4.0213769558006023</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B99">
         <v>3</v>
@@ -4462,11 +4502,11 @@
       <c r="G99">
         <v>117.0080622160648</v>
       </c>
-      <c r="H99">
-        <v>0.05668385878300081</v>
-      </c>
-      <c r="I99">
-        <v>43.60275290162583</v>
+      <c r="H99" s="6">
+        <v>0.93843127648638203</v>
+      </c>
+      <c r="I99" s="2">
+        <v>4.2031193270855773</v>
       </c>
       <c r="J99">
         <v>2</v>
@@ -4475,15 +4515,15 @@
         <v>4</v>
       </c>
       <c r="L99">
-        <v>0.007258613950332681</v>
-      </c>
-      <c r="M99">
-        <v>2.514014239037708</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13">
+        <v>7.2586139503326812E-3</v>
+      </c>
+      <c r="M99" s="4">
+        <v>2.878855855624697</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B100">
         <v>5</v>
@@ -4503,11 +4543,11 @@
       <c r="G100">
         <v>142.4603541113332</v>
       </c>
-      <c r="H100">
-        <v>0.3359662461566613</v>
-      </c>
-      <c r="I100">
-        <v>53.07043185804615</v>
+      <c r="H100" s="6">
+        <v>0.91455217961150004</v>
+      </c>
+      <c r="I100" s="2">
+        <v>4.9226776847980211</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -4516,15 +4556,15 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>0.00490166037320525</v>
-      </c>
-      <c r="M100">
-        <v>2.735978830230696</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13">
+        <v>4.9016603732052501E-3</v>
+      </c>
+      <c r="M100" s="4">
+        <v>4.5392741643998429</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B101">
         <v>4</v>
@@ -4542,13 +4582,13 @@
         <v>4</v>
       </c>
       <c r="G101">
-        <v>163.920022863446</v>
-      </c>
-      <c r="H101">
-        <v>0.365810003810228</v>
-      </c>
-      <c r="I101">
-        <v>69.33609595906863</v>
+        <v>163.92002286344601</v>
+      </c>
+      <c r="H101" s="6">
+        <v>0.6142574255423443</v>
+      </c>
+      <c r="I101" s="2">
+        <v>2.3588042395040012</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -4557,10 +4597,10 @@
         <v>0</v>
       </c>
       <c r="L101">
-        <v>0.005329315785151775</v>
-      </c>
-      <c r="M101">
-        <v>2.77896514888154</v>
+        <v>5.3293157851517746E-3</v>
+      </c>
+      <c r="M101" s="4">
+        <v>4.7480414001932987</v>
       </c>
     </row>
   </sheetData>
